--- a/data/publication_delay.xlsx
+++ b/data/publication_delay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timotheedangleterre/Desktop/ENSAE/Semestre 1/ESSD/ProjetESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1850C202-92EB-884A-90CF-1F43B731353E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D5BE9A-0B45-5444-ADC1-51210A467034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32020" yWindow="2120" windowWidth="28800" windowHeight="16480" activeTab="2" xr2:uid="{46034075-2372-374E-B1C1-96809F874CEA}"/>
+    <workbookView xWindow="32020" yWindow="2120" windowWidth="28800" windowHeight="16480" activeTab="3" xr2:uid="{46034075-2372-374E-B1C1-96809F874CEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Germany" sheetId="1" r:id="rId1"/>
@@ -41,28 +41,24 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={9587A5C1-0988-DD4B-B21B-598C10EA489F}</author>
-    <author>tc={0457328F-5C49-6D4F-B8EE-4E5EFBFE2B52}</author>
-    <author>tc={82C77C7F-04C2-B84F-A29B-0A6879BB844F}</author>
-    <author>tc={6FB9D1B5-83F1-894B-8EF4-DB4BEE955490}</author>
-    <author>tc={E0C67BCB-1A19-F942-B6A8-19C7A3CDF0A5}</author>
-    <author>tc={364DC410-6278-0B47-AC48-CF8F8FB6E5E8}</author>
-    <author>tc={8BF34D05-2848-4F4F-8C76-9775B21A76C5}</author>
-    <author>tc={3EED13DE-B909-9C4C-931D-D3098522BE8A}</author>
-    <author>tc={5C1FA7C4-3FF4-1043-86BE-C0CC4244BF55}</author>
-    <author>tc={0E60CCF1-4844-EC4E-BF0C-137DB8D9BD42}</author>
-    <author>tc={031EB594-B683-594F-9E19-67C204963A6C}</author>
-    <author>tc={E4C99FEF-88FA-2649-941F-44670933F3CD}</author>
-    <author>tc={887534EB-B146-2F45-8670-747675F48E7E}</author>
-    <author>tc={A9D038E2-4EF5-854B-9F01-DD9693DAE517}</author>
-    <author>tc={047C7B8D-B4A4-BC46-BC00-3CAB3574785F}</author>
-    <author>tc={CAEBA97A-BE10-C04B-AA56-3703B689C9C8}</author>
-    <author>tc={76002723-E7DC-EC4F-A739-C67EE1E2EC8F}</author>
-    <author>tc={06CD5E11-BB06-734C-83CE-4CEEBBE97919}</author>
-    <author>tc={7A1DB719-23BF-7449-AB6C-3D590E903207}</author>
+    <author>tc={8587559F-4BFC-1D4F-B14B-BA321EE79A76}</author>
+    <author>tc={014A890B-1C17-9444-BC60-3F179A23D6CD}</author>
+    <author>tc={5AA99D5E-852F-234E-A5D9-C86630E8035A}</author>
+    <author>tc={2E3F139A-031D-D24A-BF1F-28303CEADB8D}</author>
+    <author>tc={9D297454-F1F1-4046-A705-05AAA16603FF}</author>
+    <author>tc={DAF4C8C9-44EB-5847-94A6-6B10A7666F66}</author>
+    <author>tc={A933625E-E45E-5546-875B-6CB14AC7380C}</author>
+    <author>tc={5239BBDC-49D1-124C-AE0A-92BFF3D1D09A}</author>
+    <author>tc={A4BA6F4E-60EF-2F46-AFF9-09949A6B60B1}</author>
+    <author>tc={C5D20B24-7564-5D47-A956-87679C4A2370}</author>
+    <author>tc={A455F7CA-2EE9-D746-9B9D-F1BCBDA2614F}</author>
+    <author>tc={51073DA7-B5D6-E24E-ADA1-4E8E785296F5}</author>
+    <author>tc={2A81262F-DE66-194C-9D8A-C3BF9EFDDBF5}</author>
+    <author>tc={9B9A9E95-E7B9-3044-BAF9-699C9903F331}</author>
+    <author>tc={CA20818C-6B11-B642-9C44-27C8E583A02C}</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{9587A5C1-0988-DD4B-B21B-598C10EA489F}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{8587559F-4BFC-1D4F-B14B-BA321EE79A76}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,7 +66,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{0457328F-5C49-6D4F-B8EE-4E5EFBFE2B52}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{014A890B-1C17-9444-BC60-3F179A23D6CD}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -81,7 +77,7 @@
 https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{82C77C7F-04C2-B84F-A29B-0A6879BB844F}">
+    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{5AA99D5E-852F-234E-A5D9-C86630E8035A}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -89,7 +85,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="3" shapeId="0" xr:uid="{6FB9D1B5-83F1-894B-8EF4-DB4BEE955490}">
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{2E3F139A-031D-D24A-BF1F-28303CEADB8D}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -104,7 +100,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="J1" authorId="4" shapeId="0" xr:uid="{E0C67BCB-1A19-F942-B6A8-19C7A3CDF0A5}">
+    <comment ref="K1" authorId="4" shapeId="0" xr:uid="{9D297454-F1F1-4046-A705-05AAA16603FF}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -112,7 +108,7 @@
     Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="5" shapeId="0" xr:uid="{364DC410-6278-0B47-AC48-CF8F8FB6E5E8}">
+    <comment ref="L1" authorId="5" shapeId="0" xr:uid="{DAF4C8C9-44EB-5847-94A6-6B10A7666F66}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -120,7 +116,7 @@
     Dbnomics Energy prices</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="6" shapeId="0" xr:uid="{8BF34D05-2848-4F4F-8C76-9775B21A76C5}">
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{A933625E-E45E-5546-875B-6CB14AC7380C}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -128,7 +124,7 @@
     Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="7" shapeId="0" xr:uid="{3EED13DE-B909-9C4C-931D-D3098522BE8A}">
+    <comment ref="O1" authorId="7" shapeId="0" xr:uid="{5239BBDC-49D1-124C-AE0A-92BFF3D1D09A}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -136,7 +132,7 @@
     Yahoo finance log returns</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="8" shapeId="0" xr:uid="{5C1FA7C4-3FF4-1043-86BE-C0CC4244BF55}">
+    <comment ref="P1" authorId="8" shapeId="0" xr:uid="{A4BA6F4E-60EF-2F46-AFF9-09949A6B60B1}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -144,7 +140,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="9" shapeId="0" xr:uid="{0E60CCF1-4844-EC4E-BF0C-137DB8D9BD42}">
+    <comment ref="Q1" authorId="9" shapeId="0" xr:uid="{C5D20B24-7564-5D47-A956-87679C4A2370}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -152,16 +148,7 @@
     IRLTLT01DEM156N</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="10" shapeId="0" xr:uid="{031EB594-B683-594F-9E19-67C204963A6C}">
-      <text>
-        <t xml:space="preserve">[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL
-</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="11" shapeId="0" xr:uid="{E4C99FEF-88FA-2649-941F-44670933F3CD}">
+    <comment ref="R1" authorId="10" shapeId="0" xr:uid="{A455F7CA-2EE9-D746-9B9D-F1BCBDA2614F}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -169,7 +156,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggdebt__custom_20213100/default/table</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="12" shapeId="0" xr:uid="{887534EB-B146-2F45-8670-747675F48E7E}">
+    <comment ref="S1" authorId="11" shapeId="0" xr:uid="{51073DA7-B5D6-E24E-ADA1-4E8E785296F5}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -178,7 +165,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="T1" authorId="13" shapeId="0" xr:uid="{A9D038E2-4EF5-854B-9F01-DD9693DAE517}">
+    <comment ref="T1" authorId="12" shapeId="0" xr:uid="{2A81262F-DE66-194C-9D8A-C3BF9EFDDBF5}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -187,7 +174,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="U1" authorId="14" shapeId="0" xr:uid="{047C7B8D-B4A4-BC46-BC00-3CAB3574785F}">
+    <comment ref="U1" authorId="13" shapeId="0" xr:uid="{9B9A9E95-E7B9-3044-BAF9-699C9903F331}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -196,47 +183,13 @@
 https://ec.europa.eu/eurostat/databrowser/view/une_ltu_q__custom_20213008/default/table</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="15" shapeId="0" xr:uid="{CAEBA97A-BE10-C04B-AA56-3703B689C9C8}">
+    <comment ref="X1" authorId="14" shapeId="0" xr:uid="{CA20818C-6B11-B642-9C44-27C8E583A02C}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     [mat,tab]=call_dbnomics('Eurostat/PRC_REM_NR/S.TOTAL.NR.DE+ES+IT+FR+EL')
 Pb avec cette commande</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="16" shapeId="0" xr:uid="{76002723-E7DC-EC4F-A739-C67EE1E2EC8F}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
-Réponse :
-    Nouvelle source (BDF) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="17" shapeId="0" xr:uid="{06CD5E11-BB06-734C-83CE-4CEEBBE97919}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    'OECD/KEI/SLRTTO01.DEU.ST.M', ...
-    'OECD/KEI/SLRTTO01.ESP.ST.M', ...
-    'OECD/KEI/SLRTTO01.ITA.ST.M', ...
-    'OECD/KEI/SLRTTO01.FRA.ST.M', ...
-    'OECD/KEI/SLRTTO01.GRC.ST.M'
-Réponse :
-    Source BDF (utilisée) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000</t>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="18" shapeId="0" xr:uid="{7A1DB719-23BF-7449-AB6C-3D590E903207}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    DEUCPIENGMINMEI</t>
       </text>
     </comment>
   </commentList>
@@ -246,28 +199,24 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={502B3376-D5E1-3245-B68F-C045EF3187DE}</author>
-    <author>tc={CF735EE7-BF1C-5747-A49A-836E32CFD037}</author>
-    <author>tc={71C2EF8A-E0F7-CC46-ABC3-C14821C836CE}</author>
-    <author>tc={6E55E389-15CA-C645-BC6A-24639A10EFFE}</author>
-    <author>tc={31746CA5-B108-7E4D-8307-9EA27C652920}</author>
-    <author>tc={4ECF2331-BE0C-A641-9966-D8EE17B7CA68}</author>
-    <author>tc={A5040685-0BC8-3747-B89D-AA1BE90E4447}</author>
-    <author>tc={449C7CFD-C698-E74E-B1A3-B47FBDCB70AB}</author>
-    <author>tc={7C8B76FC-0C44-3647-8CD7-77DE9901EDD7}</author>
-    <author>tc={297C65EA-9B7D-954C-A0E5-E3947D25C43B}</author>
-    <author>tc={107C8ADE-E705-2647-A95E-79A303BBF610}</author>
-    <author>tc={F0ED0075-97F7-EF44-B2CB-45966AB1348E}</author>
-    <author>tc={D4687E52-E2C2-8540-A29F-844B5A959A04}</author>
-    <author>tc={ECD8D9BD-D528-6642-9661-07FBCAE77E2D}</author>
-    <author>tc={DF9EC020-C11C-DA4F-B159-3ED6CC221654}</author>
-    <author>tc={3A4C912E-F302-D143-BEB4-4C3BA612A209}</author>
-    <author>tc={D49E80A1-C58B-FE4A-8B04-5CB1A5E7642D}</author>
-    <author>tc={1E1B5C1C-5839-FB4F-B075-6C3D3C7DABA7}</author>
-    <author>tc={A9C3417D-DFEA-9246-AF8B-E25DE529E8F6}</author>
+    <author>tc={B2B435FE-0D31-9C4F-94DF-64E6A9BBCB93}</author>
+    <author>tc={82595596-DE94-1A47-ACAB-750ED5182AA2}</author>
+    <author>tc={E08CE432-8B51-824D-B870-7844A0906F3B}</author>
+    <author>tc={8035322F-608D-AE46-AD0C-C4CE23DADCFC}</author>
+    <author>tc={C793B313-968F-004C-AA21-321F98A5E39B}</author>
+    <author>tc={3D4A1D57-6D86-FD4C-A075-D22AE062878C}</author>
+    <author>tc={5591E50F-A39C-D247-AF6C-7C03F37CA89B}</author>
+    <author>tc={6419252B-32B9-DF49-9534-EE426A391761}</author>
+    <author>tc={1F46B2E9-8600-054A-A109-3D452EE7C3F4}</author>
+    <author>tc={A53142C8-47C7-4647-9CD5-0ABF7532DD3C}</author>
+    <author>tc={C5D9599B-DF99-614F-8F3C-D173F29C78D9}</author>
+    <author>tc={B0B37451-835A-FF46-A4CC-B3DB0D7F7A51}</author>
+    <author>tc={7B193570-4177-134D-A712-D2E1C50DAE7E}</author>
+    <author>tc={2F3523A4-03FF-734C-81F1-A3C1F48F4B9B}</author>
+    <author>tc={BDC0449E-19DC-3E40-9514-F65F8D2C85CD}</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{502B3376-D5E1-3245-B68F-C045EF3187DE}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{B2B435FE-0D31-9C4F-94DF-64E6A9BBCB93}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -275,7 +224,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{CF735EE7-BF1C-5747-A49A-836E32CFD037}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{82595596-DE94-1A47-ACAB-750ED5182AA2}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -286,7 +235,7 @@
 https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{71C2EF8A-E0F7-CC46-ABC3-C14821C836CE}">
+    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{E08CE432-8B51-824D-B870-7844A0906F3B}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -294,7 +243,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="3" shapeId="0" xr:uid="{6E55E389-15CA-C645-BC6A-24639A10EFFE}">
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{8035322F-608D-AE46-AD0C-C4CE23DADCFC}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -309,7 +258,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="J1" authorId="4" shapeId="0" xr:uid="{31746CA5-B108-7E4D-8307-9EA27C652920}">
+    <comment ref="K1" authorId="4" shapeId="0" xr:uid="{C793B313-968F-004C-AA21-321F98A5E39B}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -317,7 +266,7 @@
     Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="5" shapeId="0" xr:uid="{4ECF2331-BE0C-A641-9966-D8EE17B7CA68}">
+    <comment ref="L1" authorId="5" shapeId="0" xr:uid="{3D4A1D57-6D86-FD4C-A075-D22AE062878C}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -325,7 +274,7 @@
     Dbnomics Energy prices</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="6" shapeId="0" xr:uid="{A5040685-0BC8-3747-B89D-AA1BE90E4447}">
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{5591E50F-A39C-D247-AF6C-7C03F37CA89B}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -333,7 +282,7 @@
     Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="7" shapeId="0" xr:uid="{449C7CFD-C698-E74E-B1A3-B47FBDCB70AB}">
+    <comment ref="O1" authorId="7" shapeId="0" xr:uid="{6419252B-32B9-DF49-9534-EE426A391761}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -341,7 +290,7 @@
     Yahoo finance log returns</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="8" shapeId="0" xr:uid="{7C8B76FC-0C44-3647-8CD7-77DE9901EDD7}">
+    <comment ref="P1" authorId="8" shapeId="0" xr:uid="{1F46B2E9-8600-054A-A109-3D452EE7C3F4}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -349,7 +298,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="9" shapeId="0" xr:uid="{297C65EA-9B7D-954C-A0E5-E3947D25C43B}">
+    <comment ref="Q1" authorId="9" shapeId="0" xr:uid="{A53142C8-47C7-4647-9CD5-0ABF7532DD3C}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -357,16 +306,7 @@
     IRLTLT01DEM156N</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="10" shapeId="0" xr:uid="{107C8ADE-E705-2647-A95E-79A303BBF610}">
-      <text>
-        <t xml:space="preserve">[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL
-</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="11" shapeId="0" xr:uid="{F0ED0075-97F7-EF44-B2CB-45966AB1348E}">
+    <comment ref="R1" authorId="10" shapeId="0" xr:uid="{C5D9599B-DF99-614F-8F3C-D173F29C78D9}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -374,7 +314,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggdebt__custom_20213100/default/table</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="12" shapeId="0" xr:uid="{D4687E52-E2C2-8540-A29F-844B5A959A04}">
+    <comment ref="S1" authorId="11" shapeId="0" xr:uid="{B0B37451-835A-FF46-A4CC-B3DB0D7F7A51}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -383,7 +323,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="T1" authorId="13" shapeId="0" xr:uid="{ECD8D9BD-D528-6642-9661-07FBCAE77E2D}">
+    <comment ref="T1" authorId="12" shapeId="0" xr:uid="{7B193570-4177-134D-A712-D2E1C50DAE7E}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -392,7 +332,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="U1" authorId="14" shapeId="0" xr:uid="{DF9EC020-C11C-DA4F-B159-3ED6CC221654}">
+    <comment ref="U1" authorId="13" shapeId="0" xr:uid="{2F3523A4-03FF-734C-81F1-A3C1F48F4B9B}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -401,47 +341,13 @@
 https://ec.europa.eu/eurostat/databrowser/view/une_ltu_q__custom_20213008/default/table</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="15" shapeId="0" xr:uid="{3A4C912E-F302-D143-BEB4-4C3BA612A209}">
+    <comment ref="X1" authorId="14" shapeId="0" xr:uid="{BDC0449E-19DC-3E40-9514-F65F8D2C85CD}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     [mat,tab]=call_dbnomics('Eurostat/PRC_REM_NR/S.TOTAL.NR.DE+ES+IT+FR+EL')
 Pb avec cette commande</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="16" shapeId="0" xr:uid="{D49E80A1-C58B-FE4A-8B04-5CB1A5E7642D}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
-Réponse :
-    Nouvelle source (BDF) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="17" shapeId="0" xr:uid="{1E1B5C1C-5839-FB4F-B075-6C3D3C7DABA7}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    'OECD/KEI/SLRTTO01.DEU.ST.M', ...
-    'OECD/KEI/SLRTTO01.ESP.ST.M', ...
-    'OECD/KEI/SLRTTO01.ITA.ST.M', ...
-    'OECD/KEI/SLRTTO01.FRA.ST.M', ...
-    'OECD/KEI/SLRTTO01.GRC.ST.M'
-Réponse :
-    Source BDF (utilisée) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000</t>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="18" shapeId="0" xr:uid="{A9C3417D-DFEA-9246-AF8B-E25DE529E8F6}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    DEUCPIENGMINMEI</t>
       </text>
     </comment>
   </commentList>
@@ -609,28 +515,24 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={F3112ADC-5968-1345-A10C-166F69C55A25}</author>
-    <author>tc={F48EE2BC-CB23-9C4F-8842-2E72551D9E1E}</author>
-    <author>tc={49178015-38D1-0540-8C75-C2A85CBFE93C}</author>
-    <author>tc={6CEE85F6-F000-B146-9036-0CC70DB6D6AF}</author>
-    <author>tc={97527E90-C067-EB40-9E3A-1132E76739A0}</author>
-    <author>tc={13C6B741-E5A2-C64D-BACA-7EB872AFB715}</author>
-    <author>tc={3384B57A-B475-184D-A88A-A63EB8AA5E71}</author>
-    <author>tc={229CC063-6D46-A24D-941C-DBEAEB542359}</author>
-    <author>tc={D2EB1AAE-0AC2-3844-9596-7F4746D0081D}</author>
-    <author>tc={8CF714D5-3C21-9345-95C5-6AA4839C03B8}</author>
-    <author>tc={2EB36055-D007-A84B-9BAB-B4ECADB6F509}</author>
-    <author>tc={99CEF0F9-BC1A-6045-97B6-5B09462124AD}</author>
-    <author>tc={4D1D3A59-5A8D-F546-B5A9-5B10BA457D58}</author>
-    <author>tc={86797F79-32D1-EC40-9455-DEF6F2027611}</author>
-    <author>tc={02C1A596-DE46-1C48-9A44-E101567FD09E}</author>
-    <author>tc={0A02AB4B-F24D-F047-B588-FE2A9C8ABBD0}</author>
-    <author>tc={AAEEDD0F-5451-9A4A-93D6-CCD191835170}</author>
-    <author>tc={2BB42E58-28ED-2A44-9D0D-D20581131AF8}</author>
-    <author>tc={3D8DD456-059D-954E-B463-96C14D3F39AD}</author>
+    <author>tc={85E06548-334E-B34F-91FA-1A1D40095CA4}</author>
+    <author>tc={F7709185-9B97-164D-B4FC-FEA1C362AF6D}</author>
+    <author>tc={F756D6BD-F040-5843-AEC9-7A9E74D86330}</author>
+    <author>tc={A90A5AAF-10A7-1B48-8B31-AF717DF6D859}</author>
+    <author>tc={BB3B2C19-4A6B-E745-8CFA-CC6DBB9FCB2B}</author>
+    <author>tc={8129E3B2-1FD2-894B-B644-EE9D21C33BE3}</author>
+    <author>tc={2A6EF710-8623-B443-963B-F4677ACA73E7}</author>
+    <author>tc={20A4F8D4-9198-174E-83EB-3D7A9C39F354}</author>
+    <author>tc={C5C495E2-6714-0D43-8BAE-BE97032B7D36}</author>
+    <author>tc={AB50EE0E-0745-624D-B60D-4889D2739E5F}</author>
+    <author>tc={79BC7CD8-55D6-694F-BA7F-BD77C1DECB77}</author>
+    <author>tc={A5A09009-62E0-9147-9A82-DECE050298CC}</author>
+    <author>tc={27CA2C08-42FB-EE48-A42C-47672B71AB92}</author>
+    <author>tc={0779DDC0-9DD6-F745-897D-E986686E3E16}</author>
+    <author>tc={0E8B51D0-3017-8745-AAF0-EB224B8DA1E3}</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F3112ADC-5968-1345-A10C-166F69C55A25}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{85E06548-334E-B34F-91FA-1A1D40095CA4}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -638,7 +540,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{F48EE2BC-CB23-9C4F-8842-2E72551D9E1E}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{F7709185-9B97-164D-B4FC-FEA1C362AF6D}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -649,7 +551,7 @@
 https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{49178015-38D1-0540-8C75-C2A85CBFE93C}">
+    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{F756D6BD-F040-5843-AEC9-7A9E74D86330}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -657,7 +559,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="3" shapeId="0" xr:uid="{6CEE85F6-F000-B146-9036-0CC70DB6D6AF}">
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{A90A5AAF-10A7-1B48-8B31-AF717DF6D859}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -672,7 +574,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="J1" authorId="4" shapeId="0" xr:uid="{97527E90-C067-EB40-9E3A-1132E76739A0}">
+    <comment ref="K1" authorId="4" shapeId="0" xr:uid="{BB3B2C19-4A6B-E745-8CFA-CC6DBB9FCB2B}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -680,7 +582,7 @@
     Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="5" shapeId="0" xr:uid="{13C6B741-E5A2-C64D-BACA-7EB872AFB715}">
+    <comment ref="L1" authorId="5" shapeId="0" xr:uid="{8129E3B2-1FD2-894B-B644-EE9D21C33BE3}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -688,7 +590,7 @@
     Dbnomics Energy prices</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="6" shapeId="0" xr:uid="{3384B57A-B475-184D-A88A-A63EB8AA5E71}">
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{2A6EF710-8623-B443-963B-F4677ACA73E7}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -696,7 +598,7 @@
     Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="7" shapeId="0" xr:uid="{229CC063-6D46-A24D-941C-DBEAEB542359}">
+    <comment ref="O1" authorId="7" shapeId="0" xr:uid="{20A4F8D4-9198-174E-83EB-3D7A9C39F354}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -704,7 +606,7 @@
     Yahoo finance log returns</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="8" shapeId="0" xr:uid="{D2EB1AAE-0AC2-3844-9596-7F4746D0081D}">
+    <comment ref="P1" authorId="8" shapeId="0" xr:uid="{C5C495E2-6714-0D43-8BAE-BE97032B7D36}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -712,7 +614,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="9" shapeId="0" xr:uid="{8CF714D5-3C21-9345-95C5-6AA4839C03B8}">
+    <comment ref="Q1" authorId="9" shapeId="0" xr:uid="{AB50EE0E-0745-624D-B60D-4889D2739E5F}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -720,16 +622,7 @@
     IRLTLT01DEM156N</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="10" shapeId="0" xr:uid="{2EB36055-D007-A84B-9BAB-B4ECADB6F509}">
-      <text>
-        <t xml:space="preserve">[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL
-</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="11" shapeId="0" xr:uid="{99CEF0F9-BC1A-6045-97B6-5B09462124AD}">
+    <comment ref="R1" authorId="10" shapeId="0" xr:uid="{79BC7CD8-55D6-694F-BA7F-BD77C1DECB77}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -737,7 +630,7 @@
     Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggdebt__custom_20213100/default/table</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="12" shapeId="0" xr:uid="{4D1D3A59-5A8D-F546-B5A9-5B10BA457D58}">
+    <comment ref="S1" authorId="11" shapeId="0" xr:uid="{A5A09009-62E0-9147-9A82-DECE050298CC}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -746,7 +639,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="T1" authorId="13" shapeId="0" xr:uid="{86797F79-32D1-EC40-9455-DEF6F2027611}">
+    <comment ref="T1" authorId="12" shapeId="0" xr:uid="{27CA2C08-42FB-EE48-A42C-47672B71AB92}">
       <text>
         <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -755,7 +648,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="U1" authorId="14" shapeId="0" xr:uid="{02C1A596-DE46-1C48-9A44-E101567FD09E}">
+    <comment ref="U1" authorId="13" shapeId="0" xr:uid="{0779DDC0-9DD6-F745-897D-E986686E3E16}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
@@ -764,47 +657,13 @@
 https://ec.europa.eu/eurostat/databrowser/view/une_ltu_q__custom_20213008/default/table</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="15" shapeId="0" xr:uid="{0A02AB4B-F24D-F047-B588-FE2A9C8ABBD0}">
+    <comment ref="X1" authorId="14" shapeId="0" xr:uid="{0E8B51D0-3017-8745-AAF0-EB224B8DA1E3}">
       <text>
         <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     [mat,tab]=call_dbnomics('Eurostat/PRC_REM_NR/S.TOTAL.NR.DE+ES+IT+FR+EL')
 Pb avec cette commande</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="16" shapeId="0" xr:uid="{AAEEDD0F-5451-9A4A-93D6-CCD191835170}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
-Réponse :
-    Nouvelle source (BDF) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="17" shapeId="0" xr:uid="{2BB42E58-28ED-2A44-9D0D-D20581131AF8}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    'OECD/KEI/SLRTTO01.DEU.ST.M', ...
-    'OECD/KEI/SLRTTO01.ESP.ST.M', ...
-    'OECD/KEI/SLRTTO01.ITA.ST.M', ...
-    'OECD/KEI/SLRTTO01.FRA.ST.M', ...
-    'OECD/KEI/SLRTTO01.GRC.ST.M'
-Réponse :
-    Source BDF (utilisée) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000</t>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="18" shapeId="0" xr:uid="{3D8DD456-059D-954E-B463-96C14D3F39AD}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    DEUCPIENGMINMEI</t>
       </text>
     </comment>
   </commentList>
@@ -812,7 +671,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="32">
   <si>
     <t>Total revenue</t>
   </si>
@@ -880,9 +739,6 @@
     <t>Public employment headcount</t>
   </si>
   <si>
-    <t>Payroll mass</t>
-  </si>
-  <si>
     <t>Sovereign credit rating revisions</t>
   </si>
   <si>
@@ -898,9 +754,6 @@
     <t>Frequency</t>
   </si>
   <si>
-    <t>First thursday</t>
-  </si>
-  <si>
     <t>Q</t>
   </si>
   <si>
@@ -913,14 +766,14 @@
     <t>Last Thursday</t>
   </si>
   <si>
-    <t>Last thursday</t>
+    <t>First Thursday</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -934,6 +787,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -962,25 +821,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1024,26 +870,24 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1384,7 +1228,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B1" dT="2026-02-22T21:01:04.78" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{9587A5C1-0988-DD4B-B21B-598C10EA489F}">
+  <threadedComment ref="B1" dT="2026-02-22T21:01:04.78" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{8587559F-4BFC-1D4F-B14B-BA321EE79A76}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1393,11 +1237,11 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-02-09T16:58:18.17" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{0457328F-5C49-6D4F-B8EE-4E5EFBFE2B52}">
+  <threadedComment ref="F1" dT="2026-02-09T16:58:18.17" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{014A890B-1C17-9444-BC60-3F179A23D6CD}">
     <text xml:space="preserve">Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
 </text>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-02-22T17:18:09.87" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{D68610D4-A28A-0043-929F-319C1E9A42EA}" parentId="{0457328F-5C49-6D4F-B8EE-4E5EFBFE2B52}">
+  <threadedComment ref="F1" dT="2026-02-22T17:18:09.87" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{891CBC36-7FB2-9944-9357-2DEC413F2B96}" parentId="{014A890B-1C17-9444-BC60-3F179A23D6CD}">
     <text>Nouvelle source (BDF) : 
 https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</text>
     <extLst>
@@ -1407,7 +1251,7 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="G1" dT="2026-02-22T16:14:00.08" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{82C77C7F-04C2-B84F-A29B-0A6879BB844F}">
+  <threadedComment ref="G1" dT="2026-02-22T16:14:00.08" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{5AA99D5E-852F-234E-A5D9-C86630E8035A}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1416,7 +1260,7 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="H1" dT="2026-02-09T17:09:30.06" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{6FB9D1B5-83F1-894B-8EF4-DB4BEE955490}">
+  <threadedComment ref="I1" dT="2026-02-09T17:09:30.06" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{2E3F139A-031D-D24A-BF1F-28303CEADB8D}">
     <text xml:space="preserve">'OECD/KEI/SLRTTO01.DEU.ST.M', ...
     'OECD/KEI/SLRTTO01.ESP.ST.M', ...
     'OECD/KEI/SLRTTO01.ITA.ST.M', ...
@@ -1424,7 +1268,7 @@
     'OECD/KEI/SLRTTO01.GRC.ST.M'
 </text>
   </threadedComment>
-  <threadedComment ref="H1" dT="2026-02-22T17:21:11.86" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{E712621E-A78F-4044-9E45-3EC4183CEDF7}" parentId="{6FB9D1B5-83F1-894B-8EF4-DB4BEE955490}">
+  <threadedComment ref="I1" dT="2026-02-22T17:21:11.86" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{D71B2870-3180-A54C-9977-BDED86B62744}" parentId="{2E3F139A-031D-D24A-BF1F-28303CEADB8D}">
     <text xml:space="preserve">Source BDF (utilisée) : https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000
 </text>
     <extLst>
@@ -1434,13 +1278,13 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="J1" dT="2026-02-09T16:45:14.15" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{E0C67BCB-1A19-F942-B6A8-19C7A3CDF0A5}">
+  <threadedComment ref="K1" dT="2026-02-09T16:45:14.15" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{9D297454-F1F1-4046-A705-05AAA16603FF}">
     <text>Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</text>
   </threadedComment>
-  <threadedComment ref="K1" dT="2026-02-09T16:19:09.52" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{364DC410-6278-0B47-AC48-CF8F8FB6E5E8}">
+  <threadedComment ref="L1" dT="2026-02-09T16:19:09.52" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{DAF4C8C9-44EB-5847-94A6-6B10A7666F66}">
     <text>Dbnomics Energy prices</text>
   </threadedComment>
-  <threadedComment ref="L1" dT="2026-02-22T22:12:48.00" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{8BF34D05-2848-4F4F-8C76-9775B21A76C5}">
+  <threadedComment ref="M1" dT="2026-02-22T22:12:48.00" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A933625E-E45E-5546-875B-6CB14AC7380C}">
     <text>Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1449,10 +1293,10 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="N1" dT="2026-02-09T16:46:20.14" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{3EED13DE-B909-9C4C-931D-D3098522BE8A}">
+  <threadedComment ref="O1" dT="2026-02-09T16:46:20.14" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{5239BBDC-49D1-124C-AE0A-92BFF3D1D09A}">
     <text>Yahoo finance log returns</text>
   </threadedComment>
-  <threadedComment ref="O1" dT="2026-02-22T21:01:18.84" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{5C1FA7C4-3FF4-1043-86BE-C0CC4244BF55}">
+  <threadedComment ref="P1" dT="2026-02-22T21:01:18.84" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A4BA6F4E-60EF-2F46-AFF9-09949A6B60B1}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1461,14 +1305,10 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="P1" dT="2026-02-09T16:20:04.23" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{0E60CCF1-4844-EC4E-BF0C-137DB8D9BD42}">
+  <threadedComment ref="Q1" dT="2026-02-09T16:20:04.23" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{C5D20B24-7564-5D47-A956-87679C4A2370}">
     <text>IRLTLT01DEM156N</text>
   </threadedComment>
-  <threadedComment ref="Q1" dT="2026-02-09T16:44:34.99" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{031EB594-B683-594F-9E19-67C204963A6C}">
-    <text xml:space="preserve">Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL
-</text>
-  </threadedComment>
-  <threadedComment ref="R1" dT="2026-02-22T17:49:17.38" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{E4C99FEF-88FA-2649-941F-44670933F3CD}">
+  <threadedComment ref="R1" dT="2026-02-22T17:49:17.38" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A455F7CA-2EE9-D746-9B9D-F1BCBDA2614F}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggdebt__custom_20213100/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1477,15 +1317,15 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="S1" dT="2026-02-09T17:24:24.53" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{887534EB-B146-2F45-8670-747675F48E7E}">
+  <threadedComment ref="S1" dT="2026-02-09T17:24:24.53" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{51073DA7-B5D6-E24E-ADA1-4E8E785296F5}">
     <text xml:space="preserve">OECD/DSD_LFS@DF_IALFS_UNE_M/DEU.UNE_LF_M.PT_LF_SUB._Z.Y._T.Y_GE15._Z.M
 </text>
   </threadedComment>
-  <threadedComment ref="T1" dT="2026-02-22T13:38:04.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A9D038E2-4EF5-854B-9F01-DD9693DAE517}">
+  <threadedComment ref="T1" dT="2026-02-22T13:38:04.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{2A81262F-DE66-194C-9D8A-C3BF9EFDDBF5}">
     <text xml:space="preserve">Données d'Eurostat, une_rt_m, désaisonnalisée, à diff pour inflow
 </text>
   </threadedComment>
-  <threadedComment ref="U1" dT="2026-02-22T17:40:00.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{047C7B8D-B4A4-BC46-BC00-3CAB3574785F}">
+  <threadedComment ref="U1" dT="2026-02-22T17:40:00.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{9B9A9E95-E7B9-3044-BAF9-699C9903F331}">
     <text>Source Eurostat/DBnomics:
 https://ec.europa.eu/eurostat/databrowser/view/une_ltu_q__custom_20213008/default/table</text>
     <extLst>
@@ -1495,15 +1335,29 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="X1" dT="2026-02-09T17:43:17.34" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{CAEBA97A-BE10-C04B-AA56-3703B689C9C8}">
+  <threadedComment ref="X1" dT="2026-02-09T17:43:17.34" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{CA20818C-6B11-B642-9C44-27C8E583A02C}">
     <text>[mat,tab]=call_dbnomics('Eurostat/PRC_REM_NR/S.TOTAL.NR.DE+ES+IT+FR+EL')
 Pb avec cette commande</text>
   </threadedComment>
-  <threadedComment ref="Y1" dT="2026-02-09T16:58:28.09" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{76002723-E7DC-EC4F-A739-C67EE1E2EC8F}">
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B1" dT="2026-02-22T21:01:04.78" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{B2B435FE-0D31-9C4F-94DF-64E6A9BBCB93}">
+    <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2135100724</xltc2:checksum>
+        <xltc2:hyperlink startIndex="10" length="91" url="https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="F1" dT="2026-02-09T16:58:18.17" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{82595596-DE94-1A47-ACAB-750ED5182AA2}">
     <text xml:space="preserve">Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
 </text>
   </threadedComment>
-  <threadedComment ref="Y1" dT="2026-02-22T17:18:16.59" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{D28A1240-6E05-224B-B9E8-7A106259F5BF}" parentId="{76002723-E7DC-EC4F-A739-C67EE1E2EC8F}">
+  <threadedComment ref="F1" dT="2026-02-22T17:18:09.87" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{6F5932EF-B5FD-AC45-9226-2EAEBB04A823}" parentId="{82595596-DE94-1A47-ACAB-750ED5182AA2}">
     <text>Nouvelle source (BDF) : 
 https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</text>
     <extLst>
@@ -1513,7 +1367,16 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="Z1" dT="2026-02-09T17:09:45.74" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{06CD5E11-BB06-734C-83CE-4CEEBBE97919}">
+  <threadedComment ref="G1" dT="2026-02-22T16:14:00.08" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{E08CE432-8B51-824D-B870-7844A0906F3B}">
+    <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>289947849</xltc2:checksum>
+        <xltc2:hyperlink startIndex="10" length="88" url="https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2026-02-09T17:09:30.06" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{8035322F-608D-AE46-AD0C-C4CE23DADCFC}">
     <text xml:space="preserve">'OECD/KEI/SLRTTO01.DEU.ST.M', ...
     'OECD/KEI/SLRTTO01.ESP.ST.M', ...
     'OECD/KEI/SLRTTO01.ITA.ST.M', ...
@@ -1521,25 +1384,35 @@
     'OECD/KEI/SLRTTO01.GRC.ST.M'
 </text>
   </threadedComment>
-  <threadedComment ref="Z1" dT="2026-02-22T17:21:23.18" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{0321DBCC-45A1-F34B-8A2A-D186A7DEFB7B}" parentId="{06CD5E11-BB06-734C-83CE-4CEEBBE97919}">
-    <text>Source BDF (utilisée) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3562568072</xltc2:checksum>
-        <xltc2:hyperlink startIndex="25" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="AC1" dT="2026-02-09T16:14:06.77" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{7A1DB719-23BF-7449-AB6C-3D590E903207}">
-    <text>DEUCPIENGMINMEI</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B1" dT="2026-02-22T21:01:04.78" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{502B3376-D5E1-3245-B68F-C045EF3187DE}">
+  <threadedComment ref="I1" dT="2026-02-22T17:21:11.86" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{FE6F24A0-1CE8-5942-8CCB-500C40C81813}" parentId="{8035322F-608D-AE46-AD0C-C4CE23DADCFC}">
+    <text xml:space="preserve">Source BDF (utilisée) : https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000
+</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1477247759</xltc2:checksum>
+        <xltc2:hyperlink startIndex="24" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="K1" dT="2026-02-09T16:45:14.15" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{C793B313-968F-004C-AA21-321F98A5E39B}">
+    <text>Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</text>
+  </threadedComment>
+  <threadedComment ref="L1" dT="2026-02-09T16:19:09.52" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{3D4A1D57-6D86-FD4C-A075-D22AE062878C}">
+    <text>Dbnomics Energy prices</text>
+  </threadedComment>
+  <threadedComment ref="M1" dT="2026-02-22T22:12:48.00" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{5591E50F-A39C-D247-AF6C-7C03F37CA89B}">
+    <text>Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>3212066654</xltc2:checksum>
+        <xltc2:hyperlink startIndex="34" length="81" url="https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="O1" dT="2026-02-09T16:46:20.14" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{6419252B-32B9-DF49-9534-EE426A391761}">
+    <text>Yahoo finance log returns</text>
+  </threadedComment>
+  <threadedComment ref="P1" dT="2026-02-22T21:01:18.84" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{1F46B2E9-8600-054A-A109-3D452EE7C3F4}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1548,82 +1421,10 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-02-09T16:58:18.17" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{CF735EE7-BF1C-5747-A49A-836E32CFD037}">
-    <text xml:space="preserve">Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
-</text>
-  </threadedComment>
-  <threadedComment ref="F1" dT="2026-02-22T17:18:09.87" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{38DDDF43-47E5-5E47-BD0B-B80331DF74C7}" parentId="{CF735EE7-BF1C-5747-A49A-836E32CFD037}">
-    <text>Nouvelle source (BDF) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>2587719474</xltc2:checksum>
-        <xltc2:hyperlink startIndex="25" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="G1" dT="2026-02-22T16:14:00.08" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{71C2EF8A-E0F7-CC46-ABC3-C14821C836CE}">
-    <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>289947849</xltc2:checksum>
-        <xltc2:hyperlink startIndex="10" length="88" url="https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="H1" dT="2026-02-09T17:09:30.06" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{6E55E389-15CA-C645-BC6A-24639A10EFFE}">
-    <text xml:space="preserve">'OECD/KEI/SLRTTO01.DEU.ST.M', ...
-    'OECD/KEI/SLRTTO01.ESP.ST.M', ...
-    'OECD/KEI/SLRTTO01.ITA.ST.M', ...
-    'OECD/KEI/SLRTTO01.FRA.ST.M', ...
-    'OECD/KEI/SLRTTO01.GRC.ST.M'
-</text>
-  </threadedComment>
-  <threadedComment ref="H1" dT="2026-02-22T17:21:11.86" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A7F0E84D-E1C6-9B4E-A1AB-80CA51B09C1C}" parentId="{6E55E389-15CA-C645-BC6A-24639A10EFFE}">
-    <text xml:space="preserve">Source BDF (utilisée) : https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000
-</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>1477247759</xltc2:checksum>
-        <xltc2:hyperlink startIndex="24" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="J1" dT="2026-02-09T16:45:14.15" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{31746CA5-B108-7E4D-8307-9EA27C652920}">
-    <text>Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</text>
-  </threadedComment>
-  <threadedComment ref="K1" dT="2026-02-09T16:19:09.52" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{4ECF2331-BE0C-A641-9966-D8EE17B7CA68}">
-    <text>Dbnomics Energy prices</text>
-  </threadedComment>
-  <threadedComment ref="L1" dT="2026-02-22T22:12:48.00" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A5040685-0BC8-3747-B89D-AA1BE90E4447}">
-    <text>Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3212066654</xltc2:checksum>
-        <xltc2:hyperlink startIndex="34" length="81" url="https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="N1" dT="2026-02-09T16:46:20.14" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{449C7CFD-C698-E74E-B1A3-B47FBDCB70AB}">
-    <text>Yahoo finance log returns</text>
-  </threadedComment>
-  <threadedComment ref="O1" dT="2026-02-22T21:01:18.84" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{7C8B76FC-0C44-3647-8CD7-77DE9901EDD7}">
-    <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>2135100724</xltc2:checksum>
-        <xltc2:hyperlink startIndex="10" length="91" url="https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="P1" dT="2026-02-09T16:20:04.23" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{297C65EA-9B7D-954C-A0E5-E3947D25C43B}">
+  <threadedComment ref="Q1" dT="2026-02-09T16:20:04.23" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A53142C8-47C7-4647-9CD5-0ABF7532DD3C}">
     <text>IRLTLT01DEM156N</text>
   </threadedComment>
-  <threadedComment ref="Q1" dT="2026-02-09T16:44:34.99" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{107C8ADE-E705-2647-A95E-79A303BBF610}">
-    <text xml:space="preserve">Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL
-</text>
-  </threadedComment>
-  <threadedComment ref="R1" dT="2026-02-22T17:49:17.38" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{F0ED0075-97F7-EF44-B2CB-45966AB1348E}">
+  <threadedComment ref="R1" dT="2026-02-22T17:49:17.38" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{C5D9599B-DF99-614F-8F3C-D173F29C78D9}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggdebt__custom_20213100/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1632,15 +1433,15 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="S1" dT="2026-02-09T17:24:24.53" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{D4687E52-E2C2-8540-A29F-844B5A959A04}">
+  <threadedComment ref="S1" dT="2026-02-09T17:24:24.53" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{B0B37451-835A-FF46-A4CC-B3DB0D7F7A51}">
     <text xml:space="preserve">OECD/DSD_LFS@DF_IALFS_UNE_M/DEU.UNE_LF_M.PT_LF_SUB._Z.Y._T.Y_GE15._Z.M
 </text>
   </threadedComment>
-  <threadedComment ref="T1" dT="2026-02-22T13:38:04.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{ECD8D9BD-D528-6642-9661-07FBCAE77E2D}">
+  <threadedComment ref="T1" dT="2026-02-22T13:38:04.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{7B193570-4177-134D-A712-D2E1C50DAE7E}">
     <text xml:space="preserve">Données d'Eurostat, une_rt_m, désaisonnalisée, à diff pour inflow
 </text>
   </threadedComment>
-  <threadedComment ref="U1" dT="2026-02-22T17:40:00.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{DF9EC020-C11C-DA4F-B159-3ED6CC221654}">
+  <threadedComment ref="U1" dT="2026-02-22T17:40:00.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{2F3523A4-03FF-734C-81F1-A3C1F48F4B9B}">
     <text>Source Eurostat/DBnomics:
 https://ec.europa.eu/eurostat/databrowser/view/une_ltu_q__custom_20213008/default/table</text>
     <extLst>
@@ -1650,44 +1451,9 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="X1" dT="2026-02-09T17:43:17.34" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{3A4C912E-F302-D143-BEB4-4C3BA612A209}">
+  <threadedComment ref="X1" dT="2026-02-09T17:43:17.34" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{BDC0449E-19DC-3E40-9514-F65F8D2C85CD}">
     <text>[mat,tab]=call_dbnomics('Eurostat/PRC_REM_NR/S.TOTAL.NR.DE+ES+IT+FR+EL')
 Pb avec cette commande</text>
-  </threadedComment>
-  <threadedComment ref="Y1" dT="2026-02-09T16:58:28.09" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{D49E80A1-C58B-FE4A-8B04-5CB1A5E7642D}">
-    <text xml:space="preserve">Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
-</text>
-  </threadedComment>
-  <threadedComment ref="Y1" dT="2026-02-22T17:18:16.59" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{432BF1D9-62B4-A746-AB01-15CFEBF2684C}" parentId="{D49E80A1-C58B-FE4A-8B04-5CB1A5E7642D}">
-    <text>Nouvelle source (BDF) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>2587719474</xltc2:checksum>
-        <xltc2:hyperlink startIndex="25" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="Z1" dT="2026-02-09T17:09:45.74" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{1E1B5C1C-5839-FB4F-B075-6C3D3C7DABA7}">
-    <text xml:space="preserve">'OECD/KEI/SLRTTO01.DEU.ST.M', ...
-    'OECD/KEI/SLRTTO01.ESP.ST.M', ...
-    'OECD/KEI/SLRTTO01.ITA.ST.M', ...
-    'OECD/KEI/SLRTTO01.FRA.ST.M', ...
-    'OECD/KEI/SLRTTO01.GRC.ST.M'
-</text>
-  </threadedComment>
-  <threadedComment ref="Z1" dT="2026-02-22T17:21:23.18" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{CC86A025-019E-3943-87C3-8250D281A668}" parentId="{1E1B5C1C-5839-FB4F-B075-6C3D3C7DABA7}">
-    <text>Source BDF (utilisée) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3562568072</xltc2:checksum>
-        <xltc2:hyperlink startIndex="25" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="AC1" dT="2026-02-09T16:14:06.77" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A9C3417D-DFEA-9246-AF8B-E25DE529E8F6}">
-    <text>DEUCPIENGMINMEI</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1810,7 +1576,7 @@
 
 <file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B1" dT="2026-02-22T21:01:04.78" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{F3112ADC-5968-1345-A10C-166F69C55A25}">
+  <threadedComment ref="B1" dT="2026-02-22T21:01:04.78" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{85E06548-334E-B34F-91FA-1A1D40095CA4}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1819,11 +1585,11 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-02-09T16:58:18.17" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{F48EE2BC-CB23-9C4F-8842-2E72551D9E1E}">
+  <threadedComment ref="F1" dT="2026-02-09T16:58:18.17" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{F7709185-9B97-164D-B4FC-FEA1C362AF6D}">
     <text xml:space="preserve">Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
 </text>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-02-22T17:18:09.87" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{9ABF65AA-A760-1542-996B-AA13C227FA3C}" parentId="{F48EE2BC-CB23-9C4F-8842-2E72551D9E1E}">
+  <threadedComment ref="F1" dT="2026-02-22T17:18:09.87" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{65A606BC-2B1C-6649-BF04-0F2405D158B6}" parentId="{F7709185-9B97-164D-B4FC-FEA1C362AF6D}">
     <text>Nouvelle source (BDF) : 
 https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</text>
     <extLst>
@@ -1833,7 +1599,7 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="G1" dT="2026-02-22T16:14:00.08" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{49178015-38D1-0540-8C75-C2A85CBFE93C}">
+  <threadedComment ref="G1" dT="2026-02-22T16:14:00.08" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{F756D6BD-F040-5843-AEC9-7A9E74D86330}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/sts_intv_m__custom_20212487/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1842,7 +1608,7 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="H1" dT="2026-02-09T17:09:30.06" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{6CEE85F6-F000-B146-9036-0CC70DB6D6AF}">
+  <threadedComment ref="I1" dT="2026-02-09T17:09:30.06" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A90A5AAF-10A7-1B48-8B31-AF717DF6D859}">
     <text xml:space="preserve">'OECD/KEI/SLRTTO01.DEU.ST.M', ...
     'OECD/KEI/SLRTTO01.ESP.ST.M', ...
     'OECD/KEI/SLRTTO01.ITA.ST.M', ...
@@ -1850,7 +1616,7 @@
     'OECD/KEI/SLRTTO01.GRC.ST.M'
 </text>
   </threadedComment>
-  <threadedComment ref="H1" dT="2026-02-22T17:21:11.86" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{5C0828B8-3A2F-854B-85DD-0B4612AEB455}" parentId="{6CEE85F6-F000-B146-9036-0CC70DB6D6AF}">
+  <threadedComment ref="I1" dT="2026-02-22T17:21:11.86" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{32F55BEB-9EE9-F540-AA7A-EBBA80DEAB29}" parentId="{A90A5AAF-10A7-1B48-8B31-AF717DF6D859}">
     <text xml:space="preserve">Source BDF (utilisée) : https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000
 </text>
     <extLst>
@@ -1860,13 +1626,13 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="J1" dT="2026-02-09T16:45:14.15" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{97527E90-C067-EB40-9E3A-1132E76739A0}">
+  <threadedComment ref="K1" dT="2026-02-09T16:45:14.15" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{BB3B2C19-4A6B-E745-8CFA-CC6DBB9FCB2B}">
     <text>Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL</text>
   </threadedComment>
-  <threadedComment ref="K1" dT="2026-02-09T16:19:09.52" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{13C6B741-E5A2-C64D-BACA-7EB872AFB715}">
+  <threadedComment ref="L1" dT="2026-02-09T16:19:09.52" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{8129E3B2-1FD2-894B-B644-EE9D21C33BE3}">
     <text>Dbnomics Energy prices</text>
   </threadedComment>
-  <threadedComment ref="L1" dT="2026-02-22T22:12:48.00" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{3384B57A-B475-184D-A88A-A63EB8AA5E71}">
+  <threadedComment ref="M1" dT="2026-02-22T22:12:48.00" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{2A6EF710-8623-B443-963B-F4677ACA73E7}">
     <text>Employment in Germany ; Destatis: https://www-genesis.destatis.de/datenbank/online/statistic/13321/table/13321-0001</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1875,10 +1641,10 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="N1" dT="2026-02-09T16:46:20.14" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{229CC063-6D46-A24D-941C-DBEAEB542359}">
+  <threadedComment ref="O1" dT="2026-02-09T16:46:20.14" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{20A4F8D4-9198-174E-83EB-3D7A9C39F354}">
     <text>Yahoo finance log returns</text>
   </threadedComment>
-  <threadedComment ref="O1" dT="2026-02-22T21:01:18.84" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{D2EB1AAE-0AC2-3844-9596-7F4746D0081D}">
+  <threadedComment ref="P1" dT="2026-02-22T21:01:18.84" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{C5C495E2-6714-0D43-8BAE-BE97032B7D36}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggnfa__custom_20213168/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1887,14 +1653,10 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="P1" dT="2026-02-09T16:20:04.23" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{8CF714D5-3C21-9345-95C5-6AA4839C03B8}">
+  <threadedComment ref="Q1" dT="2026-02-09T16:20:04.23" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{AB50EE0E-0745-624D-B60D-4889D2739E5F}">
     <text>IRLTLT01DEM156N</text>
   </threadedComment>
-  <threadedComment ref="Q1" dT="2026-02-09T16:44:34.99" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{2EB36055-D007-A84B-9BAB-B4ECADB6F509}">
-    <text xml:space="preserve">Eurostat/prc_hicp_manr/M.RCH_A.TOT_X_NRG.DE+ES+IT+FR+EL
-</text>
-  </threadedComment>
-  <threadedComment ref="R1" dT="2026-02-22T17:49:17.38" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{99CEF0F9-BC1A-6045-97B6-5B09462124AD}">
+  <threadedComment ref="R1" dT="2026-02-22T17:49:17.38" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{79BC7CD8-55D6-694F-BA7F-BD77C1DECB77}">
     <text>Eurostat: https://ec.europa.eu/eurostat/databrowser/view/gov_10q_ggdebt__custom_20213100/default/table</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1903,15 +1665,15 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="S1" dT="2026-02-09T17:24:24.53" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{4D1D3A59-5A8D-F546-B5A9-5B10BA457D58}">
+  <threadedComment ref="S1" dT="2026-02-09T17:24:24.53" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{A5A09009-62E0-9147-9A82-DECE050298CC}">
     <text xml:space="preserve">OECD/DSD_LFS@DF_IALFS_UNE_M/DEU.UNE_LF_M.PT_LF_SUB._Z.Y._T.Y_GE15._Z.M
 </text>
   </threadedComment>
-  <threadedComment ref="T1" dT="2026-02-22T13:38:04.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{86797F79-32D1-EC40-9455-DEF6F2027611}">
+  <threadedComment ref="T1" dT="2026-02-22T13:38:04.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{27CA2C08-42FB-EE48-A42C-47672B71AB92}">
     <text xml:space="preserve">Données d'Eurostat, une_rt_m, désaisonnalisée, à diff pour inflow
 </text>
   </threadedComment>
-  <threadedComment ref="U1" dT="2026-02-22T17:40:00.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{02C1A596-DE46-1C48-9A44-E101567FD09E}">
+  <threadedComment ref="U1" dT="2026-02-22T17:40:00.22" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{0779DDC0-9DD6-F745-897D-E986686E3E16}">
     <text>Source Eurostat/DBnomics:
 https://ec.europa.eu/eurostat/databrowser/view/une_ltu_q__custom_20213008/default/table</text>
     <extLst>
@@ -1921,248 +1683,183 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="X1" dT="2026-02-09T17:43:17.34" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{0A02AB4B-F24D-F047-B588-FE2A9C8ABBD0}">
+  <threadedComment ref="X1" dT="2026-02-09T17:43:17.34" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{0E8B51D0-3017-8745-AAF0-EB224B8DA1E3}">
     <text>[mat,tab]=call_dbnomics('Eurostat/PRC_REM_NR/S.TOTAL.NR.DE+ES+IT+FR+EL')
 Pb avec cette commande</text>
-  </threadedComment>
-  <threadedComment ref="Y1" dT="2026-02-09T16:58:28.09" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{AAEEDD0F-5451-9A4A-93D6-CCD191835170}">
-    <text xml:space="preserve">Eurostat/STS_INPR_M/M.PRD.B_C_X_FD_MIG_NRG.SCA.I10.DE+ES+IT+FR+EL
-</text>
-  </threadedComment>
-  <threadedComment ref="Y1" dT="2026-02-22T17:18:16.59" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{B1DFD25A-E646-8E4C-880F-293393976433}" parentId="{AAEEDD0F-5451-9A4A-93D6-CCD191835170}">
-    <text>Nouvelle source (BDF) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>2587719474</xltc2:checksum>
-        <xltc2:hyperlink startIndex="25" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.PROD.NS0020.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="Z1" dT="2026-02-09T17:09:45.74" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{2BB42E58-28ED-2A44-9D0D-D20581131AF8}">
-    <text xml:space="preserve">'OECD/KEI/SLRTTO01.DEU.ST.M', ...
-    'OECD/KEI/SLRTTO01.ESP.ST.M', ...
-    'OECD/KEI/SLRTTO01.ITA.ST.M', ...
-    'OECD/KEI/SLRTTO01.FRA.ST.M', ...
-    'OECD/KEI/SLRTTO01.GRC.ST.M'
-</text>
-  </threadedComment>
-  <threadedComment ref="Z1" dT="2026-02-22T17:21:23.18" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{541CE8A8-288B-B24E-AFBF-90DA695C9596}" parentId="{2BB42E58-28ED-2A44-9D0D-D20581131AF8}">
-    <text>Source BDF (utilisée) : 
-https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3562568072</xltc2:checksum>
-        <xltc2:hyperlink startIndex="25" length="76" url="https://webstat.banque-france.fr/en/catalog/sts/STS.M.DE.Y.TOVV.NS4701.4.000"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="AC1" dT="2026-02-09T16:14:06.77" personId="{B6E92938-CF4F-9A42-8351-700272BBF6F3}" id="{3D8DD456-059D-954E-B463-96C14D3F39AD}">
-    <text>DEUCPIENGMINMEI</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9815CC68-7CB5-0442-8DBE-D1A9DAC9BB12}">
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
         <v>2</v>
       </c>
       <c r="D3">
@@ -2178,37 +1875,37 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3">
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>2</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -2217,39 +1914,24 @@
         <v>1</v>
       </c>
       <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
-      <c r="Z3">
-        <v>2</v>
-      </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
+        <v>2</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2270,34 +1952,34 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>27</v>
-      </c>
       <c r="K4">
         <v>27</v>
       </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4">
+      <c r="L4" s="8">
+        <v>27</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>15</v>
@@ -2311,31 +1993,16 @@
       <c r="U4">
         <v>15</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>15</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA4">
-        <v>15</v>
-      </c>
-      <c r="AB4">
-        <v>15</v>
-      </c>
-      <c r="AC4">
-        <v>27</v>
-      </c>
-      <c r="AD4" s="5">
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2347,208 +2014,171 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB5333D-AA5F-D543-9DBC-34A73B15B5C1}">
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE2" s="4"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
         <v>2</v>
       </c>
       <c r="D3">
@@ -2564,37 +2194,37 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3">
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>2</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -2603,40 +2233,24 @@
         <v>1</v>
       </c>
       <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
-      <c r="Z3">
-        <v>2</v>
-      </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2657,34 +2271,34 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>27</v>
-      </c>
       <c r="K4">
         <v>27</v>
       </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4">
+      <c r="L4" s="8">
+        <v>27</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>15</v>
@@ -2698,34 +2312,18 @@
       <c r="U4">
         <v>15</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>15</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA4">
-        <v>15</v>
-      </c>
-      <c r="AB4">
-        <v>15</v>
-      </c>
-      <c r="AC4">
-        <v>27</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="5"/>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2738,171 +2336,171 @@
   <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="24" max="24" width="10.83203125" style="5"/>
+    <col min="24" max="24" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="3" t="s">
-        <v>23</v>
+      <c r="Y1" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="8">
-        <v>2</v>
-      </c>
-      <c r="C3" s="8">
+        <v>24</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
         <v>2</v>
       </c>
       <c r="D3">
@@ -2921,21 +2519,21 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
         <v>0</v>
       </c>
       <c r="O3">
@@ -2954,27 +2552,27 @@
         <v>1</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="5">
+        <v>2</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2995,24 +2593,24 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>27</v>
-      </c>
       <c r="K4">
         <v>27</v>
       </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
+      <c r="L4" s="8">
+        <v>27</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
         <v>0</v>
       </c>
       <c r="O4">
@@ -3022,7 +2620,7 @@
         <v>15</v>
       </c>
       <c r="Q4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>15</v>
@@ -3034,18 +2632,18 @@
         <v>15</v>
       </c>
       <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="5">
+        <v>15</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3057,201 +2655,171 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AACA77B-CCFF-8A4F-8341-789E0FC2A4A6}">
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
         <v>2</v>
       </c>
       <c r="D3">
@@ -3270,34 +2838,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3">
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -3306,39 +2874,24 @@
         <v>1</v>
       </c>
       <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
-      <c r="Z3">
-        <v>2</v>
-      </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
+        <v>2</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -3359,34 +2912,34 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>27</v>
-      </c>
       <c r="K4">
         <v>27</v>
       </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4">
+      <c r="L4" s="8">
+        <v>27</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>15</v>
@@ -3400,31 +2953,16 @@
       <c r="U4">
         <v>15</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>15</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA4">
-        <v>15</v>
-      </c>
-      <c r="AB4">
-        <v>15</v>
-      </c>
-      <c r="AC4">
-        <v>27</v>
-      </c>
-      <c r="AD4" s="5">
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
         <v>0</v>
       </c>
     </row>

--- a/data/publication_delay.xlsx
+++ b/data/publication_delay.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timotheedangleterre/Desktop/ENSAE/Semestre 1/ESSD/ProjetESSD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D5BE9A-0B45-5444-ADC1-51210A467034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{03D5BE9A-0B45-5444-ADC1-51210A467034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD7D1113-4D7A-4837-A677-AE4E13DF0314}"/>
   <bookViews>
-    <workbookView xWindow="32020" yWindow="2120" windowWidth="28800" windowHeight="16480" activeTab="3" xr2:uid="{46034075-2372-374E-B1C1-96809F874CEA}"/>
+    <workbookView xWindow="30450" yWindow="-14580" windowWidth="19425" windowHeight="10305" activeTab="2" xr2:uid="{46034075-2372-374E-B1C1-96809F874CEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Germany" sheetId="1" r:id="rId1"/>
@@ -671,10 +671,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="32">
-  <si>
-    <t>Total revenue</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="34">
   <si>
     <t>Payroll Mass</t>
   </si>
@@ -712,9 +709,6 @@
     <t xml:space="preserve">Stock market </t>
   </si>
   <si>
-    <t>Total expenditure</t>
-  </si>
-  <si>
     <t>10y yield</t>
   </si>
   <si>
@@ -767,13 +761,25 @@
   </si>
   <si>
     <t>First Thursday</t>
+  </si>
+  <si>
+    <t>Total revenues accrual</t>
+  </si>
+  <si>
+    <t>Total expenditures accrual</t>
+  </si>
+  <si>
+    <t>Cash revenues</t>
+  </si>
+  <si>
+    <t>Cash expenditures</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -786,13 +792,8 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -821,7 +822,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -864,11 +865,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -888,6 +900,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1692,169 +1710,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9815CC68-7CB5-0442-8DBE-D1A9DAC9BB12}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -1928,10 +1958,16 @@
       <c r="Y3" s="4">
         <v>0</v>
       </c>
+      <c r="Z3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -1952,10 +1988,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2004,6 +2040,12 @@
       </c>
       <c r="Y4" s="4">
         <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>15</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2014,166 +2056,178 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB5333D-AA5F-D543-9DBC-34A73B15B5C1}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -2247,10 +2301,16 @@
       <c r="Y3" s="4">
         <v>0</v>
       </c>
+      <c r="Z3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2271,10 +2331,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2323,6 +2383,12 @@
       </c>
       <c r="Y4" s="4">
         <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>15</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2333,169 +2399,181 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88021672-6447-8A4F-BA83-22D41B386135}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="24" max="24" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -2569,10 +2647,16 @@
       <c r="Y3" s="4">
         <v>0</v>
       </c>
+      <c r="Z3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2593,10 +2677,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2645,6 +2729,12 @@
       </c>
       <c r="Y4" s="4">
         <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>15</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2655,166 +2745,178 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AACA77B-CCFF-8A4F-8341-789E0FC2A4A6}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -2888,10 +2990,16 @@
       <c r="Y3" s="4">
         <v>0</v>
       </c>
+      <c r="Z3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2912,10 +3020,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2964,6 +3072,12 @@
       </c>
       <c r="Y4" s="4">
         <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>15</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/publication_delay.xlsx
+++ b/data/publication_delay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{03D5BE9A-0B45-5444-ADC1-51210A467034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD7D1113-4D7A-4837-A677-AE4E13DF0314}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{03D5BE9A-0B45-5444-ADC1-51210A467034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF645356-8120-452D-B630-E042CFCBD523}"/>
   <bookViews>
-    <workbookView xWindow="30450" yWindow="-14580" windowWidth="19425" windowHeight="10305" activeTab="2" xr2:uid="{46034075-2372-374E-B1C1-96809F874CEA}"/>
+    <workbookView xWindow="28575" yWindow="-13680" windowWidth="19425" windowHeight="10305" activeTab="3" xr2:uid="{46034075-2372-374E-B1C1-96809F874CEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Germany" sheetId="1" r:id="rId1"/>
@@ -706,9 +706,6 @@
     <t>Profit share</t>
   </si>
   <si>
-    <t xml:space="preserve">Stock market </t>
-  </si>
-  <si>
     <t>10y yield</t>
   </si>
   <si>
@@ -773,6 +770,9 @@
   </si>
   <si>
     <t>Cash expenditures</t>
+  </si>
+  <si>
+    <t>Stock market</t>
   </si>
 </sst>
 </file>
@@ -900,7 +900,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1718,10 +1718,10 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1760,131 +1760,131 @@
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -1988,10 +1988,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2061,10 +2061,10 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -2103,131 +2103,131 @@
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2331,10 +2331,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2407,10 +2407,10 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -2449,131 +2449,131 @@
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -2677,10 +2677,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -2750,10 +2750,10 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -2792,131 +2792,131 @@
         <v>10</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -3020,10 +3020,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
